--- a/exports/trend_1d/SBIN_full_report.xlsx
+++ b/exports/trend_1d/SBIN_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q91"/>
+  <dimension ref="A1:U91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>7.71</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42033</v>
+        <v>42034</v>
       </c>
       <c r="H2" t="n">
-        <v>327</v>
+        <v>308.95</v>
       </c>
       <c r="I2" t="n">
         <v>309.035222424099</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K2" t="n">
-        <v>2.09</v>
+        <v>-3.54</v>
       </c>
       <c r="L2" t="n">
-        <v>2.44</v>
+        <v>4.15</v>
       </c>
       <c r="M2" t="n">
         <v>0.54</v>
       </c>
       <c r="N2" t="n">
-        <v>2.27</v>
+        <v>5.52</v>
       </c>
       <c r="O2" t="n">
         <v>5.12</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>12.33</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42103</v>
+        <v>42104</v>
       </c>
       <c r="H3" t="n">
-        <v>280.85</v>
+        <v>285.75</v>
       </c>
       <c r="I3" t="n">
         <v>284.4860093158226</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K3" t="n">
-        <v>9.1</v>
+        <v>7.51</v>
       </c>
       <c r="L3" t="n">
         <v>6.98</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>8.58</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42118</v>
+        <v>42121</v>
       </c>
       <c r="H4" t="n">
-        <v>275.55</v>
+        <v>267.05</v>
       </c>
       <c r="I4" t="n">
         <v>270.3121292579127</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.57</v>
+        <v>-6.54</v>
       </c>
       <c r="L4" t="n">
-        <v>3.99</v>
+        <v>6.88</v>
       </c>
       <c r="M4" t="n">
         <v>0.48</v>
       </c>
       <c r="N4" t="n">
-        <v>2.19</v>
+        <v>3.08</v>
       </c>
       <c r="O4" t="n">
         <v>1.74</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>11.43</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42139</v>
+        <v>42142</v>
       </c>
       <c r="H5" t="n">
-        <v>287.45</v>
+        <v>289.75</v>
       </c>
       <c r="I5" t="n">
         <v>287.6252380516274</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K5" t="n">
-        <v>-7.64</v>
+        <v>-8.5</v>
       </c>
       <c r="L5" t="n">
-        <v>7.98</v>
+        <v>8.59</v>
       </c>
       <c r="M5" t="n">
         <v>1.58</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42156</v>
+        <v>42157</v>
       </c>
       <c r="H6" t="n">
-        <v>278.2</v>
+        <v>266.25</v>
       </c>
       <c r="I6" t="n">
         <v>268.7950265375719</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.99</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>5.37</v>
+        <v>8.42</v>
       </c>
       <c r="M6" t="n">
         <v>0.8</v>
       </c>
       <c r="N6" t="n">
-        <v>2.69</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
         <v>0.8</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>11.5</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42216</v>
+        <v>42219</v>
       </c>
       <c r="H7" t="n">
-        <v>270.05</v>
+        <v>281.05</v>
       </c>
       <c r="I7" t="n">
         <v>273.9524497977068</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.43</v>
+        <v>-5.56</v>
       </c>
       <c r="L7" t="n">
-        <v>4.96</v>
+        <v>6.29</v>
       </c>
       <c r="M7" t="n">
         <v>1.27</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>9.98</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42227</v>
+        <v>42228</v>
       </c>
       <c r="H8" t="n">
-        <v>268.8</v>
+        <v>256.35</v>
       </c>
       <c r="I8" t="n">
         <v>263.0994984721036</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.36</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>4.82</v>
+        <v>9.25</v>
       </c>
       <c r="M8" t="n">
-        <v>0.19</v>
+        <v>0.5</v>
       </c>
       <c r="N8" t="n">
         <v>4.93</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>13.56</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42292</v>
+        <v>42293</v>
       </c>
       <c r="H9" t="n">
-        <v>248.95</v>
+        <v>254.85</v>
       </c>
       <c r="I9" t="n">
         <v>253.3103837065228</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K9" t="n">
-        <v>2.89</v>
+        <v>0.59</v>
       </c>
       <c r="L9" t="n">
         <v>12.35</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>8.6</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42305</v>
+        <v>42306</v>
       </c>
       <c r="H10" t="n">
-        <v>242.05</v>
+        <v>236.95</v>
       </c>
       <c r="I10" t="n">
         <v>236.9632438552752</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.02</v>
+        <v>-7.02</v>
       </c>
       <c r="L10" t="n">
-        <v>5.36</v>
+        <v>7.22</v>
       </c>
       <c r="M10" t="n">
         <v>0.46</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>8.56</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42430</v>
+        <v>42431</v>
       </c>
       <c r="H11" t="n">
-        <v>162.05</v>
+        <v>181.15</v>
       </c>
       <c r="I11" t="n">
         <v>178.3675339668197</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K11" t="n">
-        <v>31.61</v>
+        <v>23.55</v>
       </c>
       <c r="L11" t="n">
         <v>6.77</v>
       </c>
       <c r="M11" t="n">
-        <v>2.71</v>
+        <v>6.45</v>
       </c>
       <c r="N11" t="n">
-        <v>8.43</v>
+        <v>11.79</v>
       </c>
       <c r="O11" t="n">
         <v>-2.11</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>17.04</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42503</v>
+        <v>42506</v>
       </c>
       <c r="H12" t="n">
-        <v>184.85</v>
+        <v>176.8</v>
       </c>
       <c r="I12" t="n">
         <v>179.4342793723737</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K12" t="n">
-        <v>2.04</v>
+        <v>-2.4</v>
       </c>
       <c r="L12" t="n">
         <v>4.78</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>11.64</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42516</v>
+        <v>42517</v>
       </c>
       <c r="H13" t="n">
-        <v>184.15</v>
+        <v>195.9</v>
       </c>
       <c r="I13" t="n">
         <v>184.9608107763373</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.16</v>
+        <v>-10.8</v>
       </c>
       <c r="L13" t="n">
-        <v>4.92</v>
+        <v>14.48</v>
       </c>
       <c r="M13" t="n">
         <v>1.18</v>
       </c>
       <c r="N13" t="n">
-        <v>5.17</v>
+        <v>6.38</v>
       </c>
       <c r="O13" t="n">
         <v>-4.35</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>13.82</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42633</v>
+        <v>42634</v>
       </c>
       <c r="H14" t="n">
-        <v>254.45</v>
+        <v>251.15</v>
       </c>
       <c r="I14" t="n">
         <v>251.4704083090833</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K14" t="n">
-        <v>29.89</v>
+        <v>28.2</v>
       </c>
       <c r="L14" t="n">
         <v>7.35</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>7.83</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42683</v>
+        <v>42684</v>
       </c>
       <c r="H15" t="n">
-        <v>260</v>
+        <v>281.3</v>
       </c>
       <c r="I15" t="n">
         <v>261.9665999062811</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.52</v>
+        <v>-12</v>
       </c>
       <c r="L15" t="n">
-        <v>5.47</v>
+        <v>13.16</v>
       </c>
       <c r="M15" t="n">
         <v>2.69</v>
       </c>
       <c r="N15" t="n">
-        <v>4.06</v>
+        <v>8.19</v>
       </c>
       <c r="O15" t="n">
         <v>-1.3</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>12.97</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42727</v>
+        <v>42730</v>
       </c>
       <c r="H16" t="n">
-        <v>249.15</v>
+        <v>244.2</v>
       </c>
       <c r="I16" t="n">
         <v>248.1783468612855</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K16" t="n">
-        <v>-11.43</v>
+        <v>-13.19</v>
       </c>
       <c r="L16" t="n">
-        <v>11.91</v>
+        <v>13.4</v>
       </c>
       <c r="M16" t="n">
         <v>2.87</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42760</v>
+        <v>42762</v>
       </c>
       <c r="H17" t="n">
-        <v>259.2</v>
+        <v>266.45</v>
       </c>
       <c r="I17" t="n">
         <v>262.1873371691249</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K17" t="n">
-        <v>-6.14</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>7.29</v>
+        <v>9.83</v>
       </c>
       <c r="M17" t="n">
         <v>0.92</v>
       </c>
       <c r="N17" t="n">
-        <v>1.93</v>
+        <v>2.8</v>
       </c>
       <c r="O17" t="n">
         <v>-1.99</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>7.26</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42878</v>
+        <v>42879</v>
       </c>
       <c r="H18" t="n">
-        <v>288.85</v>
+        <v>283.15</v>
       </c>
       <c r="I18" t="n">
         <v>287.9106690006755</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K18" t="n">
-        <v>8.41</v>
+        <v>6.27</v>
       </c>
       <c r="L18" t="n">
         <v>2.61</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>9.619999999999999</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42929</v>
+        <v>42930</v>
       </c>
       <c r="H19" t="n">
-        <v>288.75</v>
+        <v>291.6</v>
       </c>
       <c r="I19" t="n">
         <v>290.1214010464592</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.98</v>
+        <v>-2.98</v>
       </c>
       <c r="L19" t="n">
         <v>5.95</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>6.94</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42957</v>
+        <v>42958</v>
       </c>
       <c r="H20" t="n">
-        <v>296.7</v>
+        <v>280.15</v>
       </c>
       <c r="I20" t="n">
         <v>292.7190137153742</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K20" t="n">
-        <v>1.75</v>
+        <v>-3.93</v>
       </c>
       <c r="L20" t="n">
-        <v>1.49</v>
+        <v>4.85</v>
       </c>
       <c r="M20" t="n">
-        <v>0.45</v>
+        <v>0.74</v>
       </c>
       <c r="N20" t="n">
-        <v>2.43</v>
+        <v>5.58</v>
       </c>
       <c r="O20" t="n">
         <v>0.99</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>13.51</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43032</v>
+        <v>43033</v>
       </c>
       <c r="H21" t="n">
-        <v>254.45</v>
+        <v>324.9</v>
       </c>
       <c r="I21" t="n">
         <v>260.3307635583276</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K21" t="n">
-        <v>9.17</v>
+        <v>-15.97</v>
       </c>
       <c r="L21" t="n">
-        <v>8.16</v>
+        <v>17.1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>9.98</v>
       </c>
       <c r="N21" t="n">
-        <v>3.46</v>
+        <v>27.69</v>
       </c>
       <c r="O21" t="n">
         <v>-5.58</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>17.93</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43101</v>
+        <v>43102</v>
       </c>
       <c r="H22" t="n">
-        <v>307.1</v>
+        <v>303.25</v>
       </c>
       <c r="I22" t="n">
         <v>304.1674770528278</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K22" t="n">
-        <v>-5.48</v>
+        <v>-6.66</v>
       </c>
       <c r="L22" t="n">
         <v>13.87</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>7.66</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43122</v>
+        <v>43123</v>
       </c>
       <c r="H23" t="n">
-        <v>306.5</v>
+        <v>318.1</v>
       </c>
       <c r="I23" t="n">
         <v>317.0644224898392</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.07</v>
+        <v>-4.9</v>
       </c>
       <c r="L23" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="M23" t="n">
         <v>2.57</v>
       </c>
       <c r="N23" t="n">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="O23" t="n">
         <v>-1.25</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,25 +2075,25 @@
         <v>9.279999999999999</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43136</v>
+        <v>43137</v>
       </c>
       <c r="H24" t="n">
-        <v>298.05</v>
+        <v>291.75</v>
       </c>
       <c r="I24" t="n">
         <v>296.9106119725774</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K24" t="n">
-        <v>-6.3</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>8.83</v>
+        <v>11.07</v>
       </c>
       <c r="M24" t="n">
-        <v>1.58</v>
+        <v>4.38</v>
       </c>
       <c r="N24" t="n">
         <v>5.08</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>10.16</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43199</v>
+        <v>43200</v>
       </c>
       <c r="H25" t="n">
-        <v>260.65</v>
+        <v>263.3</v>
       </c>
       <c r="I25" t="n">
         <v>260.7284627366485</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K25" t="n">
-        <v>10.66</v>
+        <v>9.75</v>
       </c>
       <c r="L25" t="n">
         <v>3.96</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>9.84</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43214</v>
+        <v>43215</v>
       </c>
       <c r="H26" t="n">
-        <v>240.6</v>
+        <v>237.2</v>
       </c>
       <c r="I26" t="n">
         <v>237.3850712197945</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K26" t="n">
-        <v>-8.619999999999999</v>
+        <v>-9.91</v>
       </c>
       <c r="L26" t="n">
-        <v>9.119999999999999</v>
+        <v>10.08</v>
       </c>
       <c r="M26" t="n">
         <v>0.64</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>8.17</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43231</v>
+        <v>43234</v>
       </c>
       <c r="H27" t="n">
-        <v>250.35</v>
+        <v>253.6</v>
       </c>
       <c r="I27" t="n">
         <v>253.5801547812075</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.54</v>
+        <v>-6.91</v>
       </c>
       <c r="L27" t="n">
-        <v>6.49</v>
+        <v>7.84</v>
       </c>
       <c r="M27" t="n">
         <v>0.91</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>7.78</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43277</v>
+        <v>43278</v>
       </c>
       <c r="H28" t="n">
-        <v>267.4</v>
+        <v>261.7</v>
       </c>
       <c r="I28" t="n">
         <v>263.9615953152569</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K28" t="n">
-        <v>5.44</v>
+        <v>3.19</v>
       </c>
       <c r="L28" t="n">
         <v>6.21</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>8.56</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43305</v>
+        <v>43306</v>
       </c>
       <c r="H29" t="n">
-        <v>266.85</v>
+        <v>271.85</v>
       </c>
       <c r="I29" t="n">
         <v>271.6012265796757</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.97</v>
+        <v>-3.88</v>
       </c>
       <c r="L29" t="n">
-        <v>2.87</v>
+        <v>4.26</v>
       </c>
       <c r="M29" t="n">
         <v>0.89</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>7.63</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43350</v>
+        <v>43353</v>
       </c>
       <c r="H30" t="n">
-        <v>291.65</v>
+        <v>284.85</v>
       </c>
       <c r="I30" t="n">
         <v>288.9315783833784</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K30" t="n">
-        <v>7.28</v>
+        <v>4.78</v>
       </c>
       <c r="L30" t="n">
         <v>2.28</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>9.83</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43403</v>
+        <v>43404</v>
       </c>
       <c r="H31" t="n">
-        <v>273.15</v>
+        <v>281.4</v>
       </c>
       <c r="I31" t="n">
         <v>276.2849732690553</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K31" t="n">
-        <v>4.11</v>
+        <v>1.21</v>
       </c>
       <c r="L31" t="n">
         <v>2.95</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>13.45</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43489</v>
+        <v>43490</v>
       </c>
       <c r="H32" t="n">
-        <v>288.05</v>
+        <v>285.4</v>
       </c>
       <c r="I32" t="n">
         <v>286.6056231279298</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K32" t="n">
-        <v>2.36</v>
+        <v>1.42</v>
       </c>
       <c r="L32" t="n">
         <v>4.64</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,25 +2696,25 @@
         <v>7.01</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43532</v>
+        <v>43535</v>
       </c>
       <c r="H33" t="n">
-        <v>281.2</v>
+        <v>287.35</v>
       </c>
       <c r="I33" t="n">
         <v>283.9904496487917</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K33" t="n">
-        <v>1.47</v>
+        <v>-0.68</v>
       </c>
       <c r="L33" t="n">
         <v>6.06</v>
       </c>
       <c r="M33" t="n">
-        <v>1.11</v>
+        <v>1.46</v>
       </c>
       <c r="N33" t="n">
         <v>2.44</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.63</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43592</v>
+        <v>43593</v>
       </c>
       <c r="H34" t="n">
-        <v>305.45</v>
+        <v>298.25</v>
       </c>
       <c r="I34" t="n">
         <v>299.8712899584803</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K34" t="n">
-        <v>6.3</v>
+        <v>3.79</v>
       </c>
       <c r="L34" t="n">
         <v>1.34</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H35" t="n">
-        <v>319.25</v>
+        <v>344.7</v>
       </c>
       <c r="I35" t="n">
         <v>319.3791631631221</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K35" t="n">
-        <v>-7.04</v>
+        <v>-15.57</v>
       </c>
       <c r="L35" t="n">
-        <v>7.95</v>
+        <v>15.94</v>
       </c>
       <c r="M35" t="n">
-        <v>0.84</v>
+        <v>3.99</v>
       </c>
       <c r="N35" t="n">
-        <v>2.92</v>
+        <v>7.97</v>
       </c>
       <c r="O35" t="n">
         <v>-2.36</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>10.63</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43668</v>
+        <v>43669</v>
       </c>
       <c r="H36" t="n">
-        <v>350.85</v>
+        <v>342.2</v>
       </c>
       <c r="I36" t="n">
         <v>350.2847531469891</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K36" t="n">
-        <v>1.78</v>
+        <v>-0.73</v>
       </c>
       <c r="L36" t="n">
         <v>3.97</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>9.42</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H37" t="n">
-        <v>274.05</v>
+        <v>301.7</v>
       </c>
       <c r="I37" t="n">
         <v>299.0493446718386</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K37" t="n">
-        <v>19.92</v>
+        <v>11.84</v>
       </c>
       <c r="L37" t="n">
         <v>3.16</v>
@@ -2550,7 +2993,7 @@
         <v>6.23</v>
       </c>
       <c r="N37" t="n">
-        <v>3.36</v>
+        <v>10.09</v>
       </c>
       <c r="O37" t="n">
         <v>-2.47</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>16.28</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43735</v>
+        <v>43738</v>
       </c>
       <c r="H38" t="n">
-        <v>281.2</v>
+        <v>270.8</v>
       </c>
       <c r="I38" t="n">
         <v>271.6137842948519</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K38" t="n">
-        <v>-6.79</v>
+        <v>-10.24</v>
       </c>
       <c r="L38" t="n">
         <v>11.04</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>15.93</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43767</v>
+        <v>43768</v>
       </c>
       <c r="H39" t="n">
-        <v>280.65</v>
+        <v>289.9</v>
       </c>
       <c r="I39" t="n">
         <v>289.330491711198</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K39" t="n">
-        <v>-3.64</v>
+        <v>-7.05</v>
       </c>
       <c r="L39" t="n">
-        <v>5.24</v>
+        <v>7.46</v>
       </c>
       <c r="M39" t="n">
         <v>1.71</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>13.59</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>43804</v>
+        <v>43805</v>
       </c>
       <c r="H40" t="n">
-        <v>336.2</v>
+        <v>320</v>
       </c>
       <c r="I40" t="n">
         <v>320.2113962208319</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K40" t="n">
-        <v>15.97</v>
+        <v>10.38</v>
       </c>
       <c r="L40" t="n">
         <v>3.67</v>
@@ -2721,7 +3200,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>3.6</v>
+        <v>4.82</v>
       </c>
       <c r="O40" t="n">
         <v>3.3</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>12.14</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>43984</v>
+        <v>43985</v>
       </c>
       <c r="H41" t="n">
-        <v>170.25</v>
+        <v>174.9</v>
       </c>
       <c r="I41" t="n">
         <v>172.0671605556057</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K41" t="n">
-        <v>46.8</v>
+        <v>45.34</v>
       </c>
       <c r="L41" t="n">
         <v>6.2</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>7</v>
+      </c>
+      <c r="U41" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>11.77</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44082</v>
+        <v>44083</v>
       </c>
       <c r="H42" t="n">
-        <v>204.05</v>
+        <v>194.85</v>
       </c>
       <c r="I42" t="n">
         <v>202.6338638254458</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K42" t="n">
-        <v>16.67</v>
+        <v>11.41</v>
       </c>
       <c r="L42" t="n">
         <v>3.23</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>12.51</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44117</v>
+        <v>44118</v>
       </c>
       <c r="H43" t="n">
-        <v>195.7</v>
+        <v>200.05</v>
       </c>
       <c r="I43" t="n">
         <v>199.8924200440495</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.44</v>
+        <v>-2.67</v>
       </c>
       <c r="L43" t="n">
         <v>5.82</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>11.18</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44218</v>
+        <v>44221</v>
       </c>
       <c r="H44" t="n">
-        <v>283.7</v>
+        <v>280.95</v>
       </c>
       <c r="I44" t="n">
         <v>281.2201840879339</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K44" t="n">
-        <v>41.81</v>
+        <v>40.44</v>
       </c>
       <c r="L44" t="n">
         <v>7.07</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>11.47</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44225</v>
+        <v>44228</v>
       </c>
       <c r="H45" t="n">
-        <v>282.1</v>
+        <v>310.7</v>
       </c>
       <c r="I45" t="n">
         <v>308.6975783860076</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.41</v>
+        <v>-10.59</v>
       </c>
       <c r="L45" t="n">
-        <v>3.45</v>
+        <v>11.73</v>
       </c>
       <c r="M45" t="n">
         <v>1.15</v>
       </c>
       <c r="N45" t="n">
-        <v>2.43</v>
+        <v>10.14</v>
       </c>
       <c r="O45" t="n">
         <v>-0.97</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>16.47</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44271</v>
+        <v>44272</v>
       </c>
       <c r="H46" t="n">
-        <v>378.55</v>
+        <v>368.15</v>
       </c>
       <c r="I46" t="n">
         <v>372.3572601285458</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K46" t="n">
-        <v>21.84</v>
+        <v>18.49</v>
       </c>
       <c r="L46" t="n">
         <v>9</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>12.26</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44327</v>
+        <v>44328</v>
       </c>
       <c r="H47" t="n">
-        <v>364.65</v>
+        <v>367.7</v>
       </c>
       <c r="I47" t="n">
         <v>367.6414493122446</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K47" t="n">
-        <v>0.95</v>
+        <v>0.12</v>
       </c>
       <c r="L47" t="n">
         <v>3.12</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>9.359999999999999</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44425</v>
+        <v>44426</v>
       </c>
       <c r="H48" t="n">
-        <v>421.5</v>
+        <v>419.7</v>
       </c>
       <c r="I48" t="n">
         <v>420.4466101392459</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K48" t="n">
-        <v>14.63</v>
+        <v>14.14</v>
       </c>
       <c r="L48" t="n">
         <v>2.22</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>7.93</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44453</v>
+        <v>44454</v>
       </c>
       <c r="H49" t="n">
-        <v>433</v>
+        <v>443.85</v>
       </c>
       <c r="I49" t="n">
         <v>440.3532318996483</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.17</v>
+        <v>-5.75</v>
       </c>
       <c r="L49" t="n">
-        <v>4.06</v>
+        <v>6.03</v>
       </c>
       <c r="M49" t="n">
         <v>1.08</v>
       </c>
       <c r="N49" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="O49" t="n">
         <v>-0.43</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.54</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H50" t="n">
-        <v>490.55</v>
+        <v>470.5</v>
       </c>
       <c r="I50" t="n">
         <v>484.5598788139509</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K50" t="n">
-        <v>10.52</v>
+        <v>6</v>
       </c>
       <c r="L50" t="n">
         <v>2.79</v>
@@ -3291,7 +3890,7 @@
         <v>1.04</v>
       </c>
       <c r="N50" t="n">
-        <v>3.67</v>
+        <v>4.09</v>
       </c>
       <c r="O50" t="n">
         <v>2.51</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>11.27</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44565</v>
+        <v>44566</v>
       </c>
       <c r="H51" t="n">
-        <v>483.5</v>
+        <v>492.4</v>
       </c>
       <c r="I51" t="n">
         <v>485.8181887441226</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.76</v>
+        <v>-4.65</v>
       </c>
       <c r="L51" t="n">
         <v>6.37</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>8.369999999999999</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H52" t="n">
-        <v>498.7</v>
+        <v>472.65</v>
       </c>
       <c r="I52" t="n">
         <v>495.679558928018</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K52" t="n">
-        <v>1.28</v>
+        <v>-4.01</v>
       </c>
       <c r="L52" t="n">
-        <v>2.69</v>
+        <v>4.96</v>
       </c>
       <c r="M52" t="n">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="N52" t="n">
         <v>5.32</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>11.63</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44635</v>
+        <v>44636</v>
       </c>
       <c r="H53" t="n">
-        <v>485.85</v>
+        <v>492.75</v>
       </c>
       <c r="I53" t="n">
         <v>485.8677401191979</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.79</v>
+        <v>-4.25</v>
       </c>
       <c r="L53" t="n">
-        <v>4.07</v>
+        <v>4.58</v>
       </c>
       <c r="M53" t="n">
         <v>4.03</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>9.779999999999999</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44683</v>
+        <v>44685</v>
       </c>
       <c r="H54" t="n">
-        <v>491</v>
+        <v>479.65</v>
       </c>
       <c r="I54" t="n">
         <v>484.7691727459234</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.36</v>
+        <v>-2.66</v>
       </c>
       <c r="L54" t="n">
         <v>3.15</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>9.949999999999999</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44743</v>
+        <v>44746</v>
       </c>
       <c r="H55" t="n">
-        <v>466.85</v>
+        <v>473.45</v>
       </c>
       <c r="I55" t="n">
         <v>471.287172666963</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K55" t="n">
-        <v>2.67</v>
+        <v>1.29</v>
       </c>
       <c r="L55" t="n">
         <v>3.5</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>6.93</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44830</v>
+        <v>44831</v>
       </c>
       <c r="H56" t="n">
-        <v>543.3</v>
+        <v>536.5</v>
       </c>
       <c r="I56" t="n">
         <v>540.9481061250408</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K56" t="n">
-        <v>14.75</v>
+        <v>13.32</v>
       </c>
       <c r="L56" t="n">
         <v>1.39</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>8.470000000000001</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44855</v>
+        <v>44858</v>
       </c>
       <c r="H57" t="n">
-        <v>560.85</v>
+        <v>570.5</v>
       </c>
       <c r="I57" t="n">
         <v>565.3372683469232</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K57" t="n">
-        <v>-4.54</v>
+        <v>-6.34</v>
       </c>
       <c r="L57" t="n">
-        <v>5.46</v>
+        <v>6.71</v>
       </c>
       <c r="M57" t="n">
         <v>2.55</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>7.19</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44915</v>
+        <v>44916</v>
       </c>
       <c r="H58" t="n">
-        <v>604.45</v>
+        <v>593.4</v>
       </c>
       <c r="I58" t="n">
         <v>595.7361632685894</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K58" t="n">
-        <v>5.95</v>
+        <v>4.01</v>
       </c>
       <c r="L58" t="n">
         <v>0.8100000000000001</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>6.22</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>44987</v>
+        <v>44988</v>
       </c>
       <c r="H59" t="n">
-        <v>533.75</v>
+        <v>561.2</v>
       </c>
       <c r="I59" t="n">
         <v>559.9209516201684</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K59" t="n">
-        <v>10.05</v>
+        <v>5.43</v>
       </c>
       <c r="L59" t="n">
         <v>4.58</v>
@@ -3804,7 +4511,7 @@
         <v>2.68</v>
       </c>
       <c r="N59" t="n">
-        <v>4.02</v>
+        <v>5.14</v>
       </c>
       <c r="O59" t="n">
         <v>-1.83</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>9.06</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>44999</v>
+        <v>45000</v>
       </c>
       <c r="H60" t="n">
-        <v>525.4</v>
+        <v>517.55</v>
       </c>
       <c r="I60" t="n">
         <v>523.844710975344</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K60" t="n">
-        <v>-6.38</v>
+        <v>-7.78</v>
       </c>
       <c r="L60" t="n">
-        <v>7.34</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="M60" t="n">
         <v>1.04</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45029</v>
+        <v>45033</v>
       </c>
       <c r="H61" t="n">
-        <v>532.95</v>
+        <v>544</v>
       </c>
       <c r="I61" t="n">
         <v>543.5365750168265</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.98</v>
+        <v>-5.11</v>
       </c>
       <c r="L61" t="n">
-        <v>3.51</v>
+        <v>5.3</v>
       </c>
       <c r="M61" t="n">
         <v>0.86</v>
       </c>
       <c r="N61" t="n">
-        <v>1.65</v>
+        <v>2.07</v>
       </c>
       <c r="O61" t="n">
         <v>-1.49</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>7.17</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45098</v>
+        <v>45099</v>
       </c>
       <c r="H62" t="n">
-        <v>566.35</v>
+        <v>562.95</v>
       </c>
       <c r="I62" t="n">
         <v>566.0165637140644</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K62" t="n">
-        <v>4.11</v>
+        <v>3.48</v>
       </c>
       <c r="L62" t="n">
         <v>2.94</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>4.3</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45107</v>
+        <v>45110</v>
       </c>
       <c r="H63" t="n">
-        <v>572.85</v>
+        <v>585.45</v>
       </c>
       <c r="I63" t="n">
         <v>578.0995600524631</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.76</v>
+        <v>-4</v>
       </c>
       <c r="L63" t="n">
-        <v>1.96</v>
+        <v>4.16</v>
       </c>
       <c r="M63" t="n">
         <v>1.09</v>
       </c>
       <c r="N63" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="O63" t="n">
         <v>-0.6</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>5</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45141</v>
+        <v>45142</v>
       </c>
       <c r="H64" t="n">
-        <v>590.5</v>
+        <v>573.3</v>
       </c>
       <c r="I64" t="n">
         <v>588.8659136211518</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K64" t="n">
-        <v>0.86</v>
+        <v>-2.08</v>
       </c>
       <c r="L64" t="n">
-        <v>1.97</v>
+        <v>2.4</v>
       </c>
       <c r="M64" t="n">
         <v>0.42</v>
       </c>
       <c r="N64" t="n">
-        <v>2.19</v>
+        <v>2.91</v>
       </c>
       <c r="O64" t="n">
         <v>2.2</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>8.67</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45181</v>
+        <v>45182</v>
       </c>
       <c r="H65" t="n">
-        <v>588.35</v>
+        <v>596.45</v>
       </c>
       <c r="I65" t="n">
         <v>592.5264894414884</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K65" t="n">
-        <v>-2.63</v>
+        <v>-4.04</v>
       </c>
       <c r="L65" t="n">
         <v>4.43</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>5.83</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45216</v>
+        <v>45217</v>
       </c>
       <c r="H66" t="n">
-        <v>576.45</v>
+        <v>572.65</v>
       </c>
       <c r="I66" t="n">
         <v>575.5483121576405</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K66" t="n">
-        <v>-3.35</v>
+        <v>-3.99</v>
       </c>
       <c r="L66" t="n">
-        <v>4.18</v>
+        <v>4.54</v>
       </c>
       <c r="M66" t="n">
         <v>1.42</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>5.23</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45232</v>
+        <v>45233</v>
       </c>
       <c r="H67" t="n">
-        <v>572.1</v>
+        <v>578.15</v>
       </c>
       <c r="I67" t="n">
         <v>577.7895535390988</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K67" t="n">
-        <v>0.1</v>
+        <v>-0.96</v>
       </c>
       <c r="L67" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="M67" t="n">
         <v>1.02</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>5.14</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45246</v>
+        <v>45247</v>
       </c>
       <c r="H68" t="n">
-        <v>584.65</v>
+        <v>563.05</v>
       </c>
       <c r="I68" t="n">
         <v>563.2944454668268</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K68" t="n">
-        <v>1.12</v>
+        <v>-2.61</v>
       </c>
       <c r="L68" t="n">
-        <v>0.96</v>
+        <v>2.78</v>
       </c>
       <c r="M68" t="n">
-        <v>0.1</v>
+        <v>1.74</v>
       </c>
       <c r="N68" t="n">
-        <v>0.66</v>
+        <v>3.69</v>
       </c>
       <c r="O68" t="n">
         <v>1.06</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>5.68</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45261</v>
+        <v>45264</v>
       </c>
       <c r="H69" t="n">
-        <v>571.75</v>
+        <v>594.7</v>
       </c>
       <c r="I69" t="n">
         <v>583.7110859066642</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.55</v>
+        <v>-5.62</v>
       </c>
       <c r="L69" t="n">
-        <v>2.03</v>
+        <v>5.85</v>
       </c>
       <c r="M69" t="n">
-        <v>0.63</v>
+        <v>2.84</v>
       </c>
       <c r="N69" t="n">
-        <v>1.24</v>
+        <v>4.01</v>
       </c>
       <c r="O69" t="n">
         <v>-3.69</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>5.26</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45311</v>
+        <v>45314</v>
       </c>
       <c r="H70" t="n">
-        <v>631.4</v>
+        <v>605.1</v>
       </c>
       <c r="I70" t="n">
         <v>615.0158204060795</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K70" t="n">
-        <v>6.17</v>
+        <v>1.75</v>
       </c>
       <c r="L70" t="n">
         <v>1.71</v>
@@ -4431,7 +5270,7 @@
         <v>2.03</v>
       </c>
       <c r="N70" t="n">
-        <v>2.89</v>
+        <v>4.17</v>
       </c>
       <c r="O70" t="n">
         <v>4.01</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>9.17</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45328</v>
+        <v>45329</v>
       </c>
       <c r="H71" t="n">
-        <v>650.25</v>
+        <v>675.25</v>
       </c>
       <c r="I71" t="n">
         <v>657.0111154531812</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K71" t="n">
-        <v>-7.46</v>
+        <v>-11.59</v>
       </c>
       <c r="L71" t="n">
-        <v>9.16</v>
+        <v>12.04</v>
       </c>
       <c r="M71" t="n">
         <v>1.02</v>
       </c>
       <c r="N71" t="n">
-        <v>2.19</v>
+        <v>3.84</v>
       </c>
       <c r="O71" t="n">
         <v>-4.17</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="H72" t="n">
-        <v>741.05</v>
+        <v>731.9</v>
       </c>
       <c r="I72" t="n">
         <v>738.9546801817833</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K72" t="n">
-        <v>9.74</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="L72" t="n">
         <v>3</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>7.84</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45406</v>
+        <v>45407</v>
       </c>
       <c r="H73" t="n">
-        <v>773.1</v>
+        <v>812.7</v>
       </c>
       <c r="I73" t="n">
         <v>780.1513072835617</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K73" t="n">
-        <v>-5.63</v>
+        <v>-11.04</v>
       </c>
       <c r="L73" t="n">
-        <v>6.67</v>
+        <v>11.27</v>
       </c>
       <c r="M73" t="n">
         <v>0.89</v>
       </c>
       <c r="N73" t="n">
-        <v>2.6</v>
+        <v>5.12</v>
       </c>
       <c r="O73" t="n">
         <v>-1.23</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>9.130000000000001</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H74" t="n">
-        <v>905.65</v>
+        <v>775.2</v>
       </c>
       <c r="I74" t="n">
         <v>814.0005713932338</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K74" t="n">
-        <v>11.44</v>
+        <v>-4.61</v>
       </c>
       <c r="L74" t="n">
-        <v>5.3</v>
+        <v>9.94</v>
       </c>
       <c r="M74" t="n">
-        <v>0.49</v>
+        <v>0.96</v>
       </c>
       <c r="N74" t="n">
-        <v>2.84</v>
+        <v>14.4</v>
       </c>
       <c r="O74" t="n">
         <v>5.12</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>19.96</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45489</v>
+        <v>45491</v>
       </c>
       <c r="H75" t="n">
-        <v>880.7</v>
+        <v>893.55</v>
       </c>
       <c r="I75" t="n">
         <v>888.7122871714805</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K75" t="n">
-        <v>-13.61</v>
+        <v>-15.27</v>
       </c>
       <c r="L75" t="n">
         <v>15.71</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,28 +5663,28 @@
         <v>6.5</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H76" t="n">
-        <v>847.85</v>
+        <v>811.65</v>
       </c>
       <c r="I76" t="n">
         <v>840.820375841828</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K76" t="n">
-        <v>-5.11</v>
+        <v>-9.17</v>
       </c>
       <c r="L76" t="n">
-        <v>5.86</v>
+        <v>10.47</v>
       </c>
       <c r="M76" t="n">
-        <v>0.89</v>
+        <v>2.11</v>
       </c>
       <c r="N76" t="n">
-        <v>1.72</v>
+        <v>4.27</v>
       </c>
       <c r="O76" t="n">
         <v>1.46</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,28 +5732,28 @@
         <v>8.24</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45593</v>
+        <v>45594</v>
       </c>
       <c r="H77" t="n">
-        <v>792.05</v>
+        <v>832.7</v>
       </c>
       <c r="I77" t="n">
         <v>822.6178494916167</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K77" t="n">
-        <v>2.41</v>
+        <v>-2.59</v>
       </c>
       <c r="L77" t="n">
-        <v>2.43</v>
+        <v>2.86</v>
       </c>
       <c r="M77" t="n">
         <v>1.42</v>
       </c>
       <c r="N77" t="n">
-        <v>2.58</v>
+        <v>5.13</v>
       </c>
       <c r="O77" t="n">
         <v>-4.27</v>
@@ -4839,7 +5762,19 @@
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>3</v>
+      </c>
+      <c r="U77" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>9.65</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>45615</v>
+        <v>45617</v>
       </c>
       <c r="H78" t="n">
-        <v>803</v>
+        <v>780.75</v>
       </c>
       <c r="I78" t="n">
         <v>798.3215496560808</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K78" t="n">
-        <v>-3.57</v>
+        <v>-6.24</v>
       </c>
       <c r="L78" t="n">
-        <v>5.07</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="M78" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="N78" t="n">
-        <v>2.47</v>
+        <v>2.77</v>
       </c>
       <c r="O78" t="n">
         <v>5.13</v>
@@ -4896,7 +5831,19 @@
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,22 +5870,22 @@
         <v>8.44</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>45628</v>
+        <v>45629</v>
       </c>
       <c r="H79" t="n">
-        <v>836.4</v>
+        <v>853.95</v>
       </c>
       <c r="I79" t="n">
         <v>846.6723071931704</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K79" t="n">
-        <v>-7.13</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>8.82</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="M79" t="n">
         <v>1.34</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,28 +5939,28 @@
         <v>7.71</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H80" t="n">
-        <v>832.8</v>
+        <v>812</v>
       </c>
       <c r="I80" t="n">
         <v>816.6358958877589</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K80" t="n">
-        <v>-2.48</v>
+        <v>-4.91</v>
       </c>
       <c r="L80" t="n">
-        <v>3.95</v>
+        <v>5.15</v>
       </c>
       <c r="M80" t="n">
         <v>1.62</v>
       </c>
       <c r="N80" t="n">
-        <v>1.46</v>
+        <v>2.5</v>
       </c>
       <c r="O80" t="n">
         <v>2.1</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S80" t="b">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -5037,19 +6008,19 @@
         <v>7.73</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="H81" t="n">
-        <v>723.15</v>
+        <v>736.7</v>
       </c>
       <c r="I81" t="n">
         <v>734.7911279420086</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K81" t="n">
-        <v>10.94</v>
+        <v>9.27</v>
       </c>
       <c r="L81" t="n">
         <v>2.96</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>4</v>
+      </c>
+      <c r="U81" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -5094,19 +6077,19 @@
         <v>6.41</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>45863</v>
+        <v>45866</v>
       </c>
       <c r="H82" t="n">
-        <v>806.55</v>
+        <v>797.15</v>
       </c>
       <c r="I82" t="n">
         <v>800.3364414201133</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K82" t="n">
-        <v>9.48</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="L82" t="n">
         <v>1.91</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>5</v>
+      </c>
+      <c r="U82" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -5151,22 +6146,22 @@
         <v>5.19</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>45882</v>
+        <v>45883</v>
       </c>
       <c r="H83" t="n">
-        <v>821.85</v>
+        <v>826.55</v>
       </c>
       <c r="I83" t="n">
         <v>824.4466816627946</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K83" t="n">
-        <v>-3.1</v>
+        <v>-3.69</v>
       </c>
       <c r="L83" t="n">
-        <v>3.56</v>
+        <v>3.87</v>
       </c>
       <c r="M83" t="n">
         <v>0.46</v>
@@ -5181,7 +6176,19 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>2</v>
+      </c>
+      <c r="U83" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -5208,19 +6215,19 @@
         <v>4.3</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="H84" t="n">
-        <v>951.05</v>
+        <v>948.1</v>
       </c>
       <c r="I84" t="n">
         <v>950.8822510009817</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K84" t="n">
-        <v>15.06</v>
+        <v>14.71</v>
       </c>
       <c r="L84" t="n">
         <v>3.39</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S84" t="b">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>5</v>
+      </c>
+      <c r="U84" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="85">
@@ -5265,22 +6284,22 @@
         <v>4.7</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="H85" t="n">
-        <v>984.75</v>
+        <v>998.95</v>
       </c>
       <c r="I85" t="n">
         <v>992.7010122707873</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K85" t="n">
-        <v>-3.87</v>
+        <v>-5.36</v>
       </c>
       <c r="L85" t="n">
-        <v>4.17</v>
+        <v>6.48</v>
       </c>
       <c r="M85" t="n">
         <v>0.46</v>
@@ -5295,7 +6314,19 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>2</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -5322,19 +6353,19 @@
         <v>3.95</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="H86" t="n">
-        <v>1169.5</v>
+        <v>1143</v>
       </c>
       <c r="I86" t="n">
         <v>1154.719808245889</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K86" t="n">
-        <v>17.07</v>
+        <v>14.42</v>
       </c>
       <c r="L86" t="n">
         <v>1.5</v>
@@ -5352,7 +6383,19 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S86" t="b">
+        <v>1</v>
+      </c>
+      <c r="T86" t="n">
+        <v>3</v>
+      </c>
+      <c r="U86" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -5379,19 +6422,19 @@
         <v>7.74</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="H87" t="n">
-        <v>1080.25</v>
+        <v>1107.85</v>
       </c>
       <c r="I87" t="n">
         <v>1097.41212809417</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K87" t="n">
-        <v>5.49</v>
+        <v>3.08</v>
       </c>
       <c r="L87" t="n">
         <v>2.3</v>
@@ -5409,7 +6452,19 @@
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R87" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S87" t="b">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>2</v>
+      </c>
+      <c r="U87" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -5436,28 +6491,28 @@
         <v>9.83</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="H88" t="n">
-        <v>1092</v>
+        <v>1019.3</v>
       </c>
       <c r="I88" t="n">
         <v>1031.22898447002</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K88" t="n">
-        <v>-1.43</v>
+        <v>-7.99</v>
       </c>
       <c r="L88" t="n">
-        <v>5.28</v>
+        <v>8.75</v>
       </c>
       <c r="M88" t="n">
         <v>1.09</v>
       </c>
       <c r="N88" t="n">
-        <v>1.85</v>
+        <v>6.66</v>
       </c>
       <c r="O88" t="n">
         <v>2.55</v>
@@ -5466,7 +6521,19 @@
         <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R88" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S88" t="b">
+        <v>1</v>
+      </c>
+      <c r="T88" t="n">
+        <v>2</v>
+      </c>
+      <c r="U88" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -5493,25 +6560,25 @@
         <v>12.59</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H89" t="n">
-        <v>1000.7</v>
+        <v>1017.15</v>
       </c>
       <c r="I89" t="n">
         <v>1014.10358778847</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K89" t="n">
-        <v>1.82</v>
+        <v>0.21</v>
       </c>
       <c r="L89" t="n">
         <v>7.43</v>
       </c>
       <c r="M89" t="n">
-        <v>1.13</v>
+        <v>1.73</v>
       </c>
       <c r="N89" t="n">
         <v>2.15</v>
@@ -5523,7 +6590,19 @@
         <v>1</v>
       </c>
       <c r="Q89" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R89" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S89" t="b">
+        <v>1</v>
+      </c>
+      <c r="T89" t="n">
+        <v>2</v>
+      </c>
+      <c r="U89" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -5550,19 +6629,19 @@
         <v>6.84</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="H90" t="n">
-        <v>1034.5</v>
+        <v>1020.9</v>
       </c>
       <c r="I90" t="n">
         <v>1033.487487706604</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K90" t="n">
-        <v>1.71</v>
+        <v>0.37</v>
       </c>
       <c r="L90" t="n">
         <v>1.61</v>
@@ -5580,7 +6659,19 @@
         <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R90" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S90" t="b">
+        <v>1</v>
+      </c>
+      <c r="T90" t="n">
+        <v>4</v>
+      </c>
+      <c r="U90" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -5631,6 +6722,14 @@
       <c r="Q91" t="n">
         <v>38</v>
       </c>
+      <c r="R91" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S91" t="b">
+        <v>1</v>
+      </c>
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10589,7 +11688,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>46.2</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="6">
@@ -10599,7 +11698,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -10609,7 +11708,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8">
@@ -10619,7 +11718,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -10629,7 +11728,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10">
@@ -10639,7 +11738,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -10649,7 +11748,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12">
@@ -10659,7 +11758,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13">
@@ -10669,7 +11768,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>39.3</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="14">
@@ -10679,7 +11778,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.05</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="15">
@@ -10689,7 +11788,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.65</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="16">
@@ -10699,7 +11798,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.41</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="17">
@@ -10709,7 +11808,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>46.8</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="18">
@@ -10719,7 +11818,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51.7</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="19">
@@ -10729,7 +11828,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.95</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="20">
@@ -10739,7 +11838,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.43</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="21">
@@ -10749,7 +11848,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.71</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="22">
@@ -10759,7 +11858,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
@@ -10769,7 +11868,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -10779,7 +11878,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="25">
@@ -10789,7 +11888,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7.1</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="26">
@@ -10799,7 +11898,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.62</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="27">
@@ -10809,7 +11908,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>13.83</v>
+        <v>27.69</v>
       </c>
     </row>
     <row r="28">
@@ -10819,7 +11918,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29">
